--- a/ecom-pdh/04_test-data/Checkout_datatest.xlsx
+++ b/ecom-pdh/04_test-data/Checkout_datatest.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t xml:space="preserve">Họ tên</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Số thẻ</t>
   </si>
   <si>
-    <t xml:space="preserve">9704 0000 0000 0018</t>
+    <t xml:space="preserve">9704000000000018</t>
   </si>
   <si>
     <t xml:space="preserve">Tên in trên thẻ</t>
@@ -86,6 +86,145 @@
   </si>
   <si>
     <t xml:space="preserve">code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông tin các dịch vụ cần test </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://staging.tongdaiwifi.vn/thiet-bi-thong-minh/camera-play-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gói lưu trữ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D FPT Camera Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7D Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chu kỳ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 tháng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 tháng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiền</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3D FPT Camera Only + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 tháng : 640.000đ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3D FPT Camera Only + 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> tháng : 880.000đ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7D Only + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 tháng : 760.000đ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7D Only + 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> tháng: 1.020.000đ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://staging.tongdaiwifi.vn/thiet-bi-thong-minh/access-point-ax1800az</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.100.000đ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://staging.tongdaiwifi.vn/thiet-bi-thong-minh/tv-samsung-ua75bu8000kxxvtest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.500.000đ</t>
   </si>
 </sst>
 </file>
@@ -97,7 +236,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd"/>
     <numFmt numFmtId="166" formatCode="m/d"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -135,6 +274,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -185,29 +331,45 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -400,145 +562,284 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="54.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="54.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>46088</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>46382</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>1234</v>
       </c>
     </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="10">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:A27"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C19" r:id="rId1" display="https://staging.tongdaiwifi.vn/thiet-bi-thong-minh/camera-play-4"/>
+    <hyperlink ref="C28" r:id="rId2" display="https://staging.tongdaiwifi.vn/thiet-bi-thong-minh/access-point-ax1800az"/>
+    <hyperlink ref="C30" r:id="rId3" display="https://staging.tongdaiwifi.vn/thiet-bi-thong-minh/tv-samsung-ua75bu8000kxxvtest"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
